--- a/settings/data/ModRacer.xlsx
+++ b/settings/data/ModRacer.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="~首页" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="车型-car" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="改件-part" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="地图-map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="~Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Car-car" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Part-part" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Map-map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Game-game" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Round-round" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Loot-loot" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="RankReward-rank_reward" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,21 +426,21 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>ModRacer 配表</t>
+          <t>ModRacer Config Tables</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>本文件为游戏数值唯一真理源头，修改后运行 ee gen-all 导出。</t>
+          <t>Single source of truth for game values. Run 'ee gen-all' after edits.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>表结构规范见 settings/tools/make_modracer_xlsx.py 头部注释。</t>
+          <t>Values/field names in English only; row 2 comments may be Chinese (not exported).</t>
         </is>
       </c>
     </row>
@@ -451,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +509,81 @@
           <t>tr_string</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -557,6 +636,81 @@
           <t>定位描述</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>铺装抓地(0-10)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>越野抗性(0-10)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>最大扭矩NM</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>最大转速rpm</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>主减速比</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>各挡齿比(|分隔)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>前轴扭矩占比(0=RWD 1=FWD)</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>最大转向角(度)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>转向速率</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>制动力倍率</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>风阻系数</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>迎风面积m2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>前轴配重(0-1)</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>重心高度偏移m</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>转动惯量倍率</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -607,6 +761,81 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>desc</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>grip_road</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>grip_offroad</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>max_torque</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>max_rpm</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>final_drive</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>gear_ratios</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>front_torque_split</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>max_steering_angle</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>steering_speed</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>brake_force_multiplier</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>coefficient_of_drag</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>frontal_area</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>front_weight_distribution</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>center_of_gravity_height_offset</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>inertia_multiplier</t>
         </is>
       </c>
     </row>
@@ -616,7 +845,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>狂暴马力型</t>
+          <t>Brute Power</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,8 +873,55 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>长直道霸主，撞击抗性好；低速易打滑，雨雪泥地操控难。</t>
-        </is>
+          <t>Straight-line monster with great impact resistance; slippery at low speed, tricky on wet/snow/mud.</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>420</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3.6|2.2|1.6|1.25|1.0|0.8</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
@@ -654,7 +930,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>灵巧敏捷型</t>
+          <t>Agile Sprinter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,8 +958,55 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>多弯赛道极其稳定，容错率高；极速上限低，直线弱。</t>
-        </is>
+          <t>Rock solid on twisty tracks with high forgiveness; low top speed, weak on straights.</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>260</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6800</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3.8|2.4|1.7|1.3|1.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -692,7 +1015,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>全能均衡型</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -720,8 +1043,55 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>起步抓地强，全地形适应好；无明显极端长板。</t>
-        </is>
+          <t>Strong launch grip and all-terrain adaptability; no extreme strengths.</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>330</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3.7|2.3|1.65|1.28|1.0|0.82</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>40</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +1189,16 @@
           <t>tr_string</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -901,6 +1281,16 @@
           <t>效果描述</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>效果枚举</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>效果强度(按effect解释)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -981,6 +1371,16 @@
       <c r="P3" t="inlineStr">
         <is>
           <t>desc</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>power</t>
         </is>
       </c>
     </row>
@@ -990,7 +1390,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>自然吸气强化引擎</t>
+          <t>NA Boost Engine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1036,8 +1436,16 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>均衡小幅提升动力。</t>
-        </is>
+          <t>Balanced mild power gain.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1046,7 +1454,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>机械增压引擎</t>
+          <t>Supercharged Engine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1092,8 +1500,16 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>中段加速凶悍，略增重量。</t>
-        </is>
+          <t>Fierce mid-range pull, slightly heavier.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1102,7 +1518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大马力涡轮引擎</t>
+          <t>Big Turbo Engine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1148,8 +1564,16 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>极限极速取向，低速扭矩迟滞。</t>
-        </is>
+          <t>Top-speed oriented, low-end lag.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1158,7 +1582,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>运动热熔胎</t>
+          <t>Sport Slicks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,8 +1628,16 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>铺装路抓地极强，越野雨雪衰减。</t>
-        </is>
+          <t>Huge asphalt grip, weak offroad/wet.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1214,7 +1646,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>拉力越野胎</t>
+          <t>Rally Offroad Tires</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1260,8 +1692,16 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>砂石泥地表现优异，极速略降。</t>
-        </is>
+          <t>Great on gravel/mud, slightly lower top speed.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1270,7 +1710,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>深纹雨胎</t>
+          <t>Deep-Tread Rain Tires</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1316,8 +1756,16 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>暴雨湿滑路面防滑利器。</t>
-        </is>
+          <t>Anti-slip on wet roads.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1326,7 +1774,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>全地形复合胎</t>
+          <t>All-Terrain Tires</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1372,8 +1820,16 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>无明显短板的全能胎。</t>
-        </is>
+          <t>No weak spot all-rounder.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1382,7 +1838,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>低阻尾翼</t>
+          <t>Low-Drag Wing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1428,8 +1884,16 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>直线减阻，冲刺极速提升。</t>
-        </is>
+          <t>Less drag, higher sprint speed.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1438,7 +1902,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>大下压力尾翼</t>
+          <t>High-Downforce Wing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1484,8 +1948,16 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>高速过弯稳定性大幅提升。</t>
-        </is>
+          <t>Much more stable in high-speed corners.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1494,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>强化悬挂</t>
+          <t>Reinforced Suspension</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1540,8 +2012,16 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>飞跳落地稳定，抗撞击。</t>
-        </is>
+          <t>Stable landings, impact resistant.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1550,7 +2030,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>轻量化底盘</t>
+          <t>Lightweight Chassis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1596,8 +2076,16 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>减重提速能，抗撞变弱。</t>
-        </is>
+          <t>Less weight, quicker, weaker to impacts.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1606,7 +2094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>火箭筒</t>
+          <t>Rocket Launcher</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1652,8 +2140,16 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>锁定前方最近车辆发射，造成减速打转。</t>
-        </is>
+          <t>Locks nearest car ahead, slows and spins it.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>slow_spin</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -1662,7 +2158,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>战术隐身</t>
+          <t>Tactical Stealth</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1708,8 +2204,16 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>半透明且无法被锁定，免疫追踪攻击。</t>
-        </is>
+          <t>Semi-transparent, untargetable, immune to tracking.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>stealth</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
@@ -1718,7 +2222,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>超级氮气</t>
+          <t>Super Nitrous</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1764,8 +2268,16 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>瞬间喷射提供极强推力。</t>
-        </is>
+          <t>Instant strong thrust burst.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>nitro_push</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1779,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,37 +2307,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>tr_string</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>string</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>tr_string</t>
         </is>
       </c>
     </row>
@@ -1842,37 +2329,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>地形</t>
+          <t>地图介绍</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>天气词缀</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>直道占比%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>弯道数</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>跳台数</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>有高风险分支</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>地图描述</t>
+          <t>天气状态</t>
         </is>
       </c>
     </row>
@@ -1889,37 +2351,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>weather</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>straight_ratio</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>corner_count</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>jump_count</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>hazard_branch</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>desc</t>
         </is>
       </c>
     </row>
@@ -1929,34 +2366,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>环湖高速公路</t>
+          <t>Lakeside Highway</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>asphalt</t>
+          <t>Long straights under open sky, top-speed heaven.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>sunny</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>70</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>长直道为主，极速车的天堂。</t>
         </is>
       </c>
     </row>
@@ -1966,34 +2386,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>砂石荒漠峡谷</t>
+          <t>Desert Gravel Canyon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gravel</t>
+          <t>Steep jumps and slippery dirt. Offroad tires and tough suspension shine.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>sandstorm</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>陡坡跳台+泥地打滑，越野胎与强化悬挂主场。</t>
         </is>
       </c>
     </row>
@@ -2003,34 +2406,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>雨雾山道</t>
+          <t>Rainy Mountain Pass</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>asphalt</t>
+          <t>Storm-soaked tight corners. Rain tires and downforce prevail.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>storm</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>30</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>暴雨湿滑连续弯，雨胎+大下压尾翼克制。</t>
         </is>
       </c>
     </row>
@@ -2040,35 +2426,739 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>冰雪极地走廊</t>
+          <t>Frozen Polar Corridor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Packed snow and ice; grip is everything.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>snow</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>参数名</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数值</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>player_max</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Max players (incl. AI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>intermission_sec</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Intermission duration (sec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>round_count</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sub-round count</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>start_countdown</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>snow</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" t="n">
+          <t>Start countdown (sec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lock_ahead_range</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rocket lock-on range ahead (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>loot_pick_radius</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Loot pickup radius (m)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tr_string</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>回合号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>回合名</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>是否决战局</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>时限秒</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>候选地图id</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>is_final</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>time_limit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>map_pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>240</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1|2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Round 2</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>270</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2|3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Round 3</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>270</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3|4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="b">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Final Showdown</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>低温积雪路面，抓地与防滑是生死线。</t>
-        </is>
+      <c r="D7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1|2|3|4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>路线类型</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>掉落点数</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>稀有度权重(r1|r2|r3|r4)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>可掉类别</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>保底稀有度(0无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>drop_count</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>rarity_weights</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>category_pool</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>guarantee_rarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>60|30|10|0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>engine|tires|aero|chassis|tactical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0|20|50|30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>engine|tires|aero|chassis|tactical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>名次</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>奖励件数</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>奖励最低稀有度</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>下回合发车位</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>reward_count</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>reward_rarity_min</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>grid_next</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
